--- a/data/raw/sales/Week 27/White_Mulberry/other_channels.xlsx
+++ b/data/raw/sales/Week 27/White_Mulberry/other_channels.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 27\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FB0472-96AB-457D-BDCB-CEA777D1B9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F0919A-F1D4-45D9-A0DF-F724A6241868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -421,10 +421,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="4">
-        <v>84764.27</v>
+        <v>127967.57</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -438,10 +438,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="4">
-        <v>53362.62</v>
+        <v>59849.9</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -455,10 +455,10 @@
         <v>4</v>
       </c>
       <c r="D4" s="4">
-        <v>28657.68</v>
+        <v>43141.97</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -472,10 +472,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="4">
-        <v>23369.49</v>
+        <v>38593.199999999997</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -489,52 +489,52 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <v>14051.71</v>
+        <v>17521.21</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="4">
-        <v>6871.19</v>
+        <v>8895.77</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>8183.9</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
